--- a/ListBrothersAr.xlsx
+++ b/ListBrothersAr.xlsx
@@ -17,16 +17,16 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'أخوة الاب'!$A$6:$J$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'أخوة الام'!$A$6:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'أخوة الام'!$A$6:$K$7</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'أخوة الاب'!$A$1:$M$51</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'أخوة الام'!$A$1:$Q$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'أخوة الام'!$A$1:$R$22</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
   <si>
     <t>العدد</t>
   </si>
@@ -74,6 +74,12 @@
   </si>
   <si>
     <t>نسبة التشابه</t>
+  </si>
+  <si>
+    <t>لقب الام</t>
+  </si>
+  <si>
+    <t>الملاحظة</t>
   </si>
 </sst>
 </file>
@@ -420,14 +426,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
@@ -435,6 +433,14 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -443,7 +449,7 @@
     <cellStyle name="Style 2" xfId="2"/>
     <cellStyle name="Style 6" xfId="3"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="33">
     <dxf>
       <font>
         <b/>
@@ -467,9 +473,7 @@
           <color indexed="64"/>
         </left>
         <right/>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
+        <top/>
         <bottom/>
         <vertical/>
         <horizontal/>
@@ -498,31 +502,61 @@
           <color indexed="64"/>
         </left>
         <right/>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="23"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="double">
           <color indexed="64"/>
@@ -1338,44 +1372,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table12" displayName="Table12" ref="A6:M7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table12" displayName="Table12" ref="A6:M7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="32" tableBorderDxfId="31" totalsRowBorderDxfId="30">
   <autoFilter ref="A6:M7"/>
   <tableColumns count="13">
-    <tableColumn id="1" name="العدد" dataDxfId="28"/>
-    <tableColumn id="2" name="اللقــــب" dataDxfId="27"/>
-    <tableColumn id="3" name="الاســــم" dataDxfId="26"/>
-    <tableColumn id="4" name="تاريخ الميلاد" dataDxfId="25"/>
-    <tableColumn id="5" name="بلــدية الميــــلاد" dataDxfId="24"/>
-    <tableColumn id="6" name="الحالة العائلية" dataDxfId="23"/>
-    <tableColumn id="7" name="اســــــــم الاب" dataDxfId="22"/>
-    <tableColumn id="8" name="اســــم الام" dataDxfId="21"/>
-    <tableColumn id="9" name=" نسبة التشابه" dataDxfId="20"/>
-    <tableColumn id="15" name="العنوان" dataDxfId="19"/>
-    <tableColumn id="13" name="تاريخ الإيداع" dataDxfId="18"/>
-    <tableColumn id="10" name="الصورة" dataDxfId="17"/>
-    <tableColumn id="12" name="رقم الملف" dataDxfId="16"/>
+    <tableColumn id="1" name="العدد" dataDxfId="29"/>
+    <tableColumn id="2" name="اللقــــب" dataDxfId="28"/>
+    <tableColumn id="3" name="الاســــم" dataDxfId="27"/>
+    <tableColumn id="4" name="تاريخ الميلاد" dataDxfId="26"/>
+    <tableColumn id="5" name="بلــدية الميــــلاد" dataDxfId="25"/>
+    <tableColumn id="6" name="الحالة العائلية" dataDxfId="24"/>
+    <tableColumn id="7" name="اســــــــم الاب" dataDxfId="23"/>
+    <tableColumn id="8" name="اســــم الام" dataDxfId="22"/>
+    <tableColumn id="9" name=" نسبة التشابه" dataDxfId="21"/>
+    <tableColumn id="15" name="العنوان" dataDxfId="20"/>
+    <tableColumn id="13" name="تاريخ الإيداع" dataDxfId="19"/>
+    <tableColumn id="10" name="الصورة" dataDxfId="18"/>
+    <tableColumn id="12" name="رقم الملف" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table1" displayName="Table1" ref="A6:M7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="15" tableBorderDxfId="14" totalsRowBorderDxfId="13">
-  <autoFilter ref="A6:M7"/>
-  <tableColumns count="13">
-    <tableColumn id="1" name="العدد" dataDxfId="12"/>
-    <tableColumn id="2" name="اللقــــب" dataDxfId="11"/>
-    <tableColumn id="3" name="الاســــم" dataDxfId="10"/>
-    <tableColumn id="4" name="تاريخ الميلاد" dataDxfId="9"/>
-    <tableColumn id="5" name="بلــدية الميــــلاد" dataDxfId="8"/>
-    <tableColumn id="6" name="الحالة العائلية" dataDxfId="7"/>
-    <tableColumn id="7" name="اســــــــم الاب" dataDxfId="6"/>
-    <tableColumn id="8" name="اســــم الام" dataDxfId="5"/>
-    <tableColumn id="9" name="نسبة التشابه" dataDxfId="4"/>
-    <tableColumn id="15" name="العنوان" dataDxfId="3"/>
-    <tableColumn id="13" name="تاريخ الإيداع" dataDxfId="2"/>
-    <tableColumn id="10" name="الصورة" dataDxfId="1"/>
-    <tableColumn id="12" name="رقم الملف" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table1" displayName="Table1" ref="A6:N7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+  <autoFilter ref="A6:N7"/>
+  <tableColumns count="14">
+    <tableColumn id="1" name="العدد" dataDxfId="13"/>
+    <tableColumn id="2" name="اللقــــب" dataDxfId="12"/>
+    <tableColumn id="3" name="الاســــم" dataDxfId="11"/>
+    <tableColumn id="4" name="تاريخ الميلاد" dataDxfId="10"/>
+    <tableColumn id="5" name="بلــدية الميــــلاد" dataDxfId="9"/>
+    <tableColumn id="6" name="الحالة العائلية" dataDxfId="8"/>
+    <tableColumn id="7" name="اســــــــم الاب" dataDxfId="7"/>
+    <tableColumn id="8" name="لقب الام" dataDxfId="6"/>
+    <tableColumn id="9" name="اســــم الام" dataDxfId="5"/>
+    <tableColumn id="13" name="تاريخ الإيداع" dataDxfId="4"/>
+    <tableColumn id="10" name="الصورة" dataDxfId="3"/>
+    <tableColumn id="14" name="رقم الملف" dataDxfId="0"/>
+    <tableColumn id="11" name="الملاحظة" dataDxfId="1"/>
+    <tableColumn id="12" name="نسبة التشابه" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1688,16 +1723,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="21"/>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
+      <c r="A1" s="24"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="B2" s="4"/>
@@ -1722,31 +1757,31 @@
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:13" s="1" customFormat="1" ht="77.25" customHeight="1">
-      <c r="A4" s="23"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24" t="s">
+      <c r="A4" s="21"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
     </row>
     <row r="5" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
     </row>
     <row r="6" spans="1:13" ht="105.75" customHeight="1" thickBot="1">
       <c r="A6" s="5" t="s">
@@ -1820,7 +1855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -1832,25 +1867,23 @@
     <col min="7" max="7" width="28.85546875" customWidth="1"/>
     <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="44.140625" customWidth="1"/>
-    <col min="11" max="11" width="25.5703125" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="26.42578125" customWidth="1"/>
+    <col min="10" max="10" width="25.5703125" customWidth="1"/>
+    <col min="11" max="13" width="25.7109375" customWidth="1"/>
+    <col min="14" max="14" width="26.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="21"/>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A1" s="24"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="B2" s="4"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3"/>
@@ -1859,9 +1892,8 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="B3" s="4"/>
       <c r="C3" s="2"/>
       <c r="D3" s="3"/>
@@ -1870,33 +1902,30 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:13" s="1" customFormat="1" ht="77.25" customHeight="1">
-      <c r="A4" s="22" t="s">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="77.25" customHeight="1">
+      <c r="A4" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
     </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
     </row>
-    <row r="6" spans="1:13" ht="105.75" customHeight="1" thickBot="1">
+    <row r="6" spans="1:14" ht="105.75" customHeight="1" thickBot="1">
       <c r="A6" s="5" t="s">
         <v>0</v>
       </c>
@@ -1919,25 +1948,28 @@
         <v>6</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="L6" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="M6" s="20" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="7" spans="1:13" ht="150" customHeight="1" thickTop="1">
+    <row r="7" spans="1:14" ht="150" customHeight="1" thickTop="1">
       <c r="A7" s="11"/>
       <c r="B7" s="12"/>
       <c r="C7" s="13"/>
@@ -1948,15 +1980,16 @@
       <c r="H7" s="12"/>
       <c r="I7" s="13"/>
       <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
+      <c r="K7" s="19"/>
       <c r="L7" s="19"/>
       <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="C5:J5"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="C5:I5"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/ListBrothersAr.xlsx
+++ b/ListBrothersAr.xlsx
@@ -9,24 +9,27 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="913" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="913"/>
   </bookViews>
   <sheets>
-    <sheet name="أخوة الاب" sheetId="47" r:id="rId1"/>
+    <sheet name="أخوة الاب" sheetId="53" r:id="rId1"/>
     <sheet name="أخوة الام" sheetId="50" r:id="rId2"/>
+    <sheet name="بلا اخوة" sheetId="52" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'أخوة الاب'!$A$6:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'أخوة الاب'!$A$6:$K$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'أخوة الام'!$A$6:$K$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'أخوة الاب'!$A$1:$M$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'بلا اخوة'!$A$6:$K$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'أخوة الاب'!$A$1:$R$22</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'أخوة الام'!$A$1:$R$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'بلا اخوة'!$A$1:$R$22</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="17">
   <si>
     <t>العدد</t>
   </si>
@@ -55,22 +58,10 @@
     <t>الصورة</t>
   </si>
   <si>
-    <t>العنوان</t>
-  </si>
-  <si>
     <t>تاريخ الإيداع</t>
   </si>
   <si>
     <t>رقم الملف</t>
-  </si>
-  <si>
-    <t>القائمـة الاسمية للاخوة</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> نسبة التشابه</t>
-  </si>
-  <si>
-    <t xml:space="preserve">القائمـة الاسمية للاخوة </t>
   </si>
   <si>
     <t>نسبة التشابه</t>
@@ -80,6 +71,15 @@
   </si>
   <si>
     <t>الملاحظة</t>
+  </si>
+  <si>
+    <t>القائمـة الاسمية للاخوة  من الام</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القائمـة الاسمية بلا اخوة </t>
+  </si>
+  <si>
+    <t>القائمـة الاسمية للاخوة  من الاب</t>
   </si>
 </sst>
 </file>
@@ -365,7 +365,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -426,13 +426,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
@@ -449,7 +449,7 @@
     <cellStyle name="Style 2" xfId="2"/>
     <cellStyle name="Style 6" xfId="3"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="51">
     <dxf>
       <font>
         <b/>
@@ -473,7 +473,9 @@
           <color indexed="64"/>
         </left>
         <right/>
-        <top/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
         <bottom/>
         <vertical/>
         <horizontal/>
@@ -531,9 +533,7 @@
           <color indexed="64"/>
         </left>
         <right/>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
+        <top/>
         <bottom/>
         <vertical/>
         <horizontal/>
@@ -890,30 +890,30 @@
     <dxf>
       <border outline="0">
         <top style="double">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom style="double">
-          <color indexed="64"/>
-        </bottom>
+          <color rgb="FF000000"/>
+        </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="double">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="double">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="double">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="double">
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
@@ -971,6 +971,64 @@
           <color indexed="64"/>
         </left>
         <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
         <top style="double">
           <color indexed="64"/>
         </top>
@@ -996,6 +1054,443 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FF2525FF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FF008600"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FF660066"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="double">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="double">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="double">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="double">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="double">
           <color indexed="64"/>
@@ -1372,29 +1867,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table12" displayName="Table12" ref="A6:M7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="32" tableBorderDxfId="31" totalsRowBorderDxfId="30">
-  <autoFilter ref="A6:M7"/>
-  <tableColumns count="13">
-    <tableColumn id="1" name="العدد" dataDxfId="29"/>
-    <tableColumn id="2" name="اللقــــب" dataDxfId="28"/>
-    <tableColumn id="3" name="الاســــم" dataDxfId="27"/>
-    <tableColumn id="4" name="تاريخ الميلاد" dataDxfId="26"/>
-    <tableColumn id="5" name="بلــدية الميــــلاد" dataDxfId="25"/>
-    <tableColumn id="6" name="الحالة العائلية" dataDxfId="24"/>
-    <tableColumn id="7" name="اســــــــم الاب" dataDxfId="23"/>
-    <tableColumn id="8" name="اســــم الام" dataDxfId="22"/>
-    <tableColumn id="9" name=" نسبة التشابه" dataDxfId="21"/>
-    <tableColumn id="15" name="العنوان" dataDxfId="20"/>
-    <tableColumn id="13" name="تاريخ الإيداع" dataDxfId="19"/>
-    <tableColumn id="10" name="الصورة" dataDxfId="18"/>
-    <tableColumn id="12" name="رقم الملف" dataDxfId="17"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table1" displayName="Table1" ref="A6:N7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table15" displayName="Table15" ref="A6:N7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
   <autoFilter ref="A6:N7"/>
   <tableColumns count="14">
     <tableColumn id="1" name="العدد" dataDxfId="13"/>
@@ -1408,9 +1881,55 @@
     <tableColumn id="9" name="اســــم الام" dataDxfId="5"/>
     <tableColumn id="13" name="تاريخ الإيداع" dataDxfId="4"/>
     <tableColumn id="10" name="الصورة" dataDxfId="3"/>
-    <tableColumn id="14" name="رقم الملف" dataDxfId="0"/>
+    <tableColumn id="14" name="رقم الملف" dataDxfId="2"/>
     <tableColumn id="11" name="الملاحظة" dataDxfId="1"/>
-    <tableColumn id="12" name="نسبة التشابه" dataDxfId="2"/>
+    <tableColumn id="12" name="نسبة التشابه" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table1" displayName="Table1" ref="A6:N7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="50" tableBorderDxfId="49" totalsRowBorderDxfId="48">
+  <autoFilter ref="A6:N7"/>
+  <tableColumns count="14">
+    <tableColumn id="1" name="العدد" dataDxfId="47"/>
+    <tableColumn id="2" name="اللقــــب" dataDxfId="46"/>
+    <tableColumn id="3" name="الاســــم" dataDxfId="45"/>
+    <tableColumn id="4" name="تاريخ الميلاد" dataDxfId="44"/>
+    <tableColumn id="5" name="بلــدية الميــــلاد" dataDxfId="43"/>
+    <tableColumn id="6" name="الحالة العائلية" dataDxfId="42"/>
+    <tableColumn id="7" name="اســــــــم الاب" dataDxfId="41"/>
+    <tableColumn id="8" name="لقب الام" dataDxfId="40"/>
+    <tableColumn id="9" name="اســــم الام" dataDxfId="39"/>
+    <tableColumn id="13" name="تاريخ الإيداع" dataDxfId="38"/>
+    <tableColumn id="10" name="الصورة" dataDxfId="37"/>
+    <tableColumn id="14" name="رقم الملف" dataDxfId="36"/>
+    <tableColumn id="11" name="الملاحظة" dataDxfId="35"/>
+    <tableColumn id="12" name="نسبة التشابه" dataDxfId="34"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="A6:N7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="33" tableBorderDxfId="32" totalsRowBorderDxfId="31">
+  <autoFilter ref="A6:N7"/>
+  <tableColumns count="14">
+    <tableColumn id="1" name="العدد" dataDxfId="30"/>
+    <tableColumn id="2" name="اللقــــب" dataDxfId="29"/>
+    <tableColumn id="3" name="الاســــم" dataDxfId="28"/>
+    <tableColumn id="4" name="تاريخ الميلاد" dataDxfId="27"/>
+    <tableColumn id="5" name="بلــدية الميــــلاد" dataDxfId="26"/>
+    <tableColumn id="6" name="الحالة العائلية" dataDxfId="25"/>
+    <tableColumn id="7" name="اســــــــم الاب" dataDxfId="24"/>
+    <tableColumn id="8" name="لقب الام" dataDxfId="23"/>
+    <tableColumn id="9" name="اســــم الام" dataDxfId="22"/>
+    <tableColumn id="13" name="تاريخ الإيداع" dataDxfId="21"/>
+    <tableColumn id="10" name="الصورة" dataDxfId="20"/>
+    <tableColumn id="14" name="رقم الملف" dataDxfId="19"/>
+    <tableColumn id="11" name="الملاحظة" dataDxfId="18"/>
+    <tableColumn id="12" name="نسبة التشابه" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1703,8 +2222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -1716,74 +2234,65 @@
     <col min="7" max="7" width="28.85546875" customWidth="1"/>
     <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="44.140625" customWidth="1"/>
-    <col min="11" max="11" width="25.5703125" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="26.42578125" customWidth="1"/>
+    <col min="10" max="10" width="25.5703125" customWidth="1"/>
+    <col min="11" max="13" width="25.7109375" customWidth="1"/>
+    <col min="14" max="14" width="26.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A1" s="23"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="B2" s="4"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="B3" s="4"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
     </row>
-    <row r="4" spans="1:13" s="1" customFormat="1" ht="77.25" customHeight="1">
-      <c r="A4" s="21"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="77.25" customHeight="1">
+      <c r="A4" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
     </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
     </row>
-    <row r="6" spans="1:13" ht="105.75" customHeight="1" thickBot="1">
+    <row r="6" spans="1:14" ht="105.75" customHeight="1" thickBot="1">
       <c r="A6" s="5" t="s">
         <v>0</v>
       </c>
@@ -1806,25 +2315,28 @@
         <v>6</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>13</v>
       </c>
       <c r="J6" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="17" t="s">
+      <c r="K6" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="20" t="s">
-        <v>8</v>
-      </c>
       <c r="M6" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="150" customHeight="1" thickTop="1">
+    <row r="7" spans="1:14" ht="150" customHeight="1" thickTop="1">
       <c r="A7" s="11"/>
       <c r="B7" s="12"/>
       <c r="C7" s="13"/>
@@ -1835,14 +2347,16 @@
       <c r="H7" s="12"/>
       <c r="I7" s="13"/>
       <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
+      <c r="K7" s="19"/>
       <c r="L7" s="19"/>
       <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C5:J5"/>
-    <mergeCell ref="A1:J1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="C5:I5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.19685039370078741" bottom="0" header="0.19685039370078741" footer="0"/>
@@ -1873,15 +2387,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="A1" s="23"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="B2" s="4"/>
@@ -1904,26 +2418,26 @@
       <c r="I3" s="3"/>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="77.25" customHeight="1">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
     </row>
     <row r="6" spans="1:14" ht="105.75" customHeight="1" thickBot="1">
       <c r="A6" s="5" t="s">
@@ -1948,25 +2462,25 @@
         <v>6</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K6" s="20" t="s">
         <v>8</v>
       </c>
       <c r="L6" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="20" t="s">
         <v>11</v>
-      </c>
-      <c r="M6" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="N6" s="20" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="150" customHeight="1" thickTop="1">
@@ -1999,4 +2513,151 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" customWidth="1"/>
+    <col min="3" max="3" width="38.5703125" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" customWidth="1"/>
+    <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5703125" customWidth="1"/>
+    <col min="11" max="13" width="25.7109375" customWidth="1"/>
+    <col min="14" max="14" width="26.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A1" s="23"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="B2" s="4"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="B3" s="4"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="77.25" customHeight="1">
+      <c r="A4" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+    </row>
+    <row r="6" spans="1:14" ht="105.75" customHeight="1" thickBot="1">
+      <c r="A6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="150" customHeight="1" thickTop="1">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="C5:I5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.19685039370078741" bottom="0" header="0.19685039370078741" footer="0"/>
+  <pageSetup paperSize="9" scale="22" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/ListBrothersAr.xlsx
+++ b/ListBrothersAr.xlsx
@@ -12,24 +12,28 @@
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="913"/>
   </bookViews>
   <sheets>
-    <sheet name="أخوة الاب" sheetId="53" r:id="rId1"/>
-    <sheet name="أخوة الام" sheetId="50" r:id="rId2"/>
-    <sheet name="بلا اخوة" sheetId="52" r:id="rId3"/>
+    <sheet name="أخوة الاشقاء" sheetId="50" r:id="rId1"/>
+    <sheet name="أخوة الاب" sheetId="53" r:id="rId2"/>
+    <sheet name="أخوة الام" sheetId="54" r:id="rId3"/>
+    <sheet name="بلا اخوة" sheetId="52" r:id="rId4"/>
+    <sheet name="احصائيات" sheetId="56" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'أخوة الاب'!$A$6:$K$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'أخوة الام'!$A$6:$K$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'بلا اخوة'!$A$6:$K$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'أخوة الاب'!$A$1:$R$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'أخوة الام'!$A$1:$R$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'بلا اخوة'!$A$1:$R$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'أخوة الاب'!$A$6:$K$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'أخوة الاشقاء'!$A$6:$K$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'أخوة الام'!$A$6:$K$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'بلا اخوة'!$A$6:$K$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'أخوة الاب'!$A$1:$Q$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'أخوة الاشقاء'!$A$1:$Q$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'أخوة الام'!$A$1:$R$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'بلا اخوة'!$A$1:$R$22</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="19">
   <si>
     <t>العدد</t>
   </si>
@@ -80,6 +84,12 @@
   </si>
   <si>
     <t>القائمـة الاسمية للاخوة  من الاب</t>
+  </si>
+  <si>
+    <t>القائمـة الاسمية للاخوة الاشقاء</t>
+  </si>
+  <si>
+    <t>عدد الاخوة</t>
   </si>
 </sst>
 </file>
@@ -237,7 +247,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -354,6 +364,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -365,7 +388,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -438,9 +461,16 @@
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -449,7 +479,7 @@
     <cellStyle name="Style 2" xfId="2"/>
     <cellStyle name="Style 6" xfId="3"/>
   </cellStyles>
-  <dxfs count="51">
+  <dxfs count="71">
     <dxf>
       <font>
         <b/>
@@ -473,9 +503,7 @@
           <color indexed="64"/>
         </left>
         <right/>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
+        <top/>
         <bottom/>
         <vertical/>
         <horizontal/>
@@ -582,6 +610,95 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
         <color theme="1"/>
         <name val="Arial"/>
         <scheme val="none"/>
@@ -892,6 +1009,22 @@
         <top style="double">
           <color rgb="FF000000"/>
         </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="double">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="double">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="double">
+          <color rgb="FF000000"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -902,16 +1035,467 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FF2525FF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FF008600"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FF660066"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
-        <left style="double">
+        <top style="double">
           <color rgb="FF000000"/>
-        </left>
-        <right style="double">
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="double">
           <color rgb="FF000000"/>
-        </right>
-        <top style="double">
+        </left>
+        <right style="double">
           <color rgb="FF000000"/>
-        </top>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="double">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="double">
           <color rgb="FF000000"/>
         </bottom>
@@ -1867,69 +2451,95 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table15" displayName="Table15" ref="A6:N7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
-  <autoFilter ref="A6:N7"/>
-  <tableColumns count="14">
-    <tableColumn id="1" name="العدد" dataDxfId="13"/>
-    <tableColumn id="2" name="اللقــــب" dataDxfId="12"/>
-    <tableColumn id="3" name="الاســــم" dataDxfId="11"/>
-    <tableColumn id="4" name="تاريخ الميلاد" dataDxfId="10"/>
-    <tableColumn id="5" name="بلــدية الميــــلاد" dataDxfId="9"/>
-    <tableColumn id="6" name="الحالة العائلية" dataDxfId="8"/>
-    <tableColumn id="7" name="اســــــــم الاب" dataDxfId="7"/>
-    <tableColumn id="8" name="لقب الام" dataDxfId="6"/>
-    <tableColumn id="9" name="اســــم الام" dataDxfId="5"/>
-    <tableColumn id="13" name="تاريخ الإيداع" dataDxfId="4"/>
-    <tableColumn id="10" name="الصورة" dataDxfId="3"/>
-    <tableColumn id="14" name="رقم الملف" dataDxfId="2"/>
-    <tableColumn id="11" name="الملاحظة" dataDxfId="1"/>
-    <tableColumn id="12" name="نسبة التشابه" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table1" displayName="Table1" ref="A6:O7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="70" tableBorderDxfId="69" totalsRowBorderDxfId="68">
+  <autoFilter ref="A6:O7"/>
+  <tableColumns count="15">
+    <tableColumn id="1" name="العدد" dataDxfId="67"/>
+    <tableColumn id="2" name="اللقــــب" dataDxfId="66"/>
+    <tableColumn id="3" name="الاســــم" dataDxfId="65"/>
+    <tableColumn id="4" name="تاريخ الميلاد" dataDxfId="64"/>
+    <tableColumn id="5" name="بلــدية الميــــلاد" dataDxfId="63"/>
+    <tableColumn id="6" name="الحالة العائلية" dataDxfId="62"/>
+    <tableColumn id="7" name="اســــــــم الاب" dataDxfId="61"/>
+    <tableColumn id="8" name="لقب الام" dataDxfId="60"/>
+    <tableColumn id="9" name="اســــم الام" dataDxfId="59"/>
+    <tableColumn id="13" name="تاريخ الإيداع" dataDxfId="58"/>
+    <tableColumn id="10" name="الصورة" dataDxfId="57"/>
+    <tableColumn id="14" name="رقم الملف" dataDxfId="56"/>
+    <tableColumn id="11" name="الملاحظة" dataDxfId="55"/>
+    <tableColumn id="12" name="نسبة التشابه" dataDxfId="54"/>
+    <tableColumn id="15" name="عدد الاخوة" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table1" displayName="Table1" ref="A6:N7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="50" tableBorderDxfId="49" totalsRowBorderDxfId="48">
-  <autoFilter ref="A6:N7"/>
-  <tableColumns count="14">
-    <tableColumn id="1" name="العدد" dataDxfId="47"/>
-    <tableColumn id="2" name="اللقــــب" dataDxfId="46"/>
-    <tableColumn id="3" name="الاســــم" dataDxfId="45"/>
-    <tableColumn id="4" name="تاريخ الميلاد" dataDxfId="44"/>
-    <tableColumn id="5" name="بلــدية الميــــلاد" dataDxfId="43"/>
-    <tableColumn id="6" name="الحالة العائلية" dataDxfId="42"/>
-    <tableColumn id="7" name="اســــــــم الاب" dataDxfId="41"/>
-    <tableColumn id="8" name="لقب الام" dataDxfId="40"/>
-    <tableColumn id="9" name="اســــم الام" dataDxfId="39"/>
-    <tableColumn id="13" name="تاريخ الإيداع" dataDxfId="38"/>
-    <tableColumn id="10" name="الصورة" dataDxfId="37"/>
-    <tableColumn id="14" name="رقم الملف" dataDxfId="36"/>
-    <tableColumn id="11" name="الملاحظة" dataDxfId="35"/>
-    <tableColumn id="12" name="نسبة التشابه" dataDxfId="34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table15" displayName="Table15" ref="A6:O7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="53" tableBorderDxfId="52" totalsRowBorderDxfId="51">
+  <autoFilter ref="A6:O7"/>
+  <tableColumns count="15">
+    <tableColumn id="1" name="العدد" dataDxfId="50"/>
+    <tableColumn id="2" name="اللقــــب" dataDxfId="49"/>
+    <tableColumn id="3" name="الاســــم" dataDxfId="48"/>
+    <tableColumn id="4" name="تاريخ الميلاد" dataDxfId="47"/>
+    <tableColumn id="5" name="بلــدية الميــــلاد" dataDxfId="46"/>
+    <tableColumn id="6" name="الحالة العائلية" dataDxfId="45"/>
+    <tableColumn id="7" name="اســــــــم الاب" dataDxfId="44"/>
+    <tableColumn id="8" name="لقب الام" dataDxfId="43"/>
+    <tableColumn id="9" name="اســــم الام" dataDxfId="42"/>
+    <tableColumn id="13" name="تاريخ الإيداع" dataDxfId="41"/>
+    <tableColumn id="10" name="الصورة" dataDxfId="40"/>
+    <tableColumn id="14" name="رقم الملف" dataDxfId="39"/>
+    <tableColumn id="11" name="الملاحظة" dataDxfId="38"/>
+    <tableColumn id="12" name="نسبة التشابه" dataDxfId="37"/>
+    <tableColumn id="15" name="عدد الاخوة" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="A6:N7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="33" tableBorderDxfId="32" totalsRowBorderDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table12" displayName="Table12" ref="A6:O7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="36" tableBorderDxfId="35" totalsRowBorderDxfId="34">
+  <autoFilter ref="A6:O7"/>
+  <tableColumns count="15">
+    <tableColumn id="1" name="العدد" dataDxfId="33"/>
+    <tableColumn id="2" name="اللقــــب" dataDxfId="32"/>
+    <tableColumn id="3" name="الاســــم" dataDxfId="31"/>
+    <tableColumn id="4" name="تاريخ الميلاد" dataDxfId="30"/>
+    <tableColumn id="5" name="بلــدية الميــــلاد" dataDxfId="29"/>
+    <tableColumn id="6" name="الحالة العائلية" dataDxfId="28"/>
+    <tableColumn id="7" name="اســــــــم الاب" dataDxfId="27"/>
+    <tableColumn id="8" name="لقب الام" dataDxfId="26"/>
+    <tableColumn id="9" name="اســــم الام" dataDxfId="25"/>
+    <tableColumn id="13" name="تاريخ الإيداع" dataDxfId="24"/>
+    <tableColumn id="10" name="الصورة" dataDxfId="23"/>
+    <tableColumn id="14" name="رقم الملف" dataDxfId="22"/>
+    <tableColumn id="11" name="الملاحظة" dataDxfId="21"/>
+    <tableColumn id="12" name="نسبة التشابه" dataDxfId="20"/>
+    <tableColumn id="15" name="عدد الاخوة" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="A6:N7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
   <autoFilter ref="A6:N7"/>
   <tableColumns count="14">
-    <tableColumn id="1" name="العدد" dataDxfId="30"/>
-    <tableColumn id="2" name="اللقــــب" dataDxfId="29"/>
-    <tableColumn id="3" name="الاســــم" dataDxfId="28"/>
-    <tableColumn id="4" name="تاريخ الميلاد" dataDxfId="27"/>
-    <tableColumn id="5" name="بلــدية الميــــلاد" dataDxfId="26"/>
-    <tableColumn id="6" name="الحالة العائلية" dataDxfId="25"/>
-    <tableColumn id="7" name="اســــــــم الاب" dataDxfId="24"/>
-    <tableColumn id="8" name="لقب الام" dataDxfId="23"/>
-    <tableColumn id="9" name="اســــم الام" dataDxfId="22"/>
-    <tableColumn id="13" name="تاريخ الإيداع" dataDxfId="21"/>
-    <tableColumn id="10" name="الصورة" dataDxfId="20"/>
-    <tableColumn id="14" name="رقم الملف" dataDxfId="19"/>
-    <tableColumn id="11" name="الملاحظة" dataDxfId="18"/>
-    <tableColumn id="12" name="نسبة التشابه" dataDxfId="17"/>
+    <tableColumn id="1" name="العدد" dataDxfId="16"/>
+    <tableColumn id="2" name="اللقــــب" dataDxfId="15"/>
+    <tableColumn id="3" name="الاســــم" dataDxfId="14"/>
+    <tableColumn id="4" name="تاريخ الميلاد" dataDxfId="13"/>
+    <tableColumn id="5" name="بلــدية الميــــلاد" dataDxfId="12"/>
+    <tableColumn id="6" name="الحالة العائلية" dataDxfId="11"/>
+    <tableColumn id="7" name="اســــــــم الاب" dataDxfId="10"/>
+    <tableColumn id="8" name="لقب الام" dataDxfId="9"/>
+    <tableColumn id="9" name="اســــم الام" dataDxfId="8"/>
+    <tableColumn id="13" name="تاريخ الإيداع" dataDxfId="7"/>
+    <tableColumn id="10" name="الصورة" dataDxfId="6"/>
+    <tableColumn id="14" name="رقم الملف" dataDxfId="5"/>
+    <tableColumn id="11" name="الملاحظة" dataDxfId="4"/>
+    <tableColumn id="12" name="نسبة التشابه" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2222,6 +2832,460 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" customWidth="1"/>
+    <col min="3" max="3" width="38.5703125" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" customWidth="1"/>
+    <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5703125" customWidth="1"/>
+    <col min="11" max="13" width="25.7109375" customWidth="1"/>
+    <col min="14" max="15" width="26.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A1" s="24"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+    </row>
+    <row r="2" spans="1:15" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="B2" s="4"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="B3" s="4"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:15" s="1" customFormat="1" ht="77.25" customHeight="1">
+      <c r="A4" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+    </row>
+    <row r="5" spans="1:15" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+    </row>
+    <row r="6" spans="1:15" ht="105.75" customHeight="1" thickBot="1">
+      <c r="A6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O6" s="26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="150" customHeight="1" thickTop="1">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="C5:I5"/>
+  </mergeCells>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.19685039370078741" bottom="0" header="0.19685039370078741" footer="0"/>
+  <pageSetup paperSize="9" scale="22" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" customWidth="1"/>
+    <col min="3" max="3" width="38.5703125" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" customWidth="1"/>
+    <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5703125" customWidth="1"/>
+    <col min="11" max="13" width="25.7109375" customWidth="1"/>
+    <col min="14" max="15" width="26.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A1" s="24"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+    </row>
+    <row r="2" spans="1:15" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="B2" s="4"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+    </row>
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="B3" s="4"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="4" spans="1:15" s="1" customFormat="1" ht="77.25" customHeight="1">
+      <c r="A4" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+    </row>
+    <row r="5" spans="1:15" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+    </row>
+    <row r="6" spans="1:15" ht="105.75" customHeight="1" thickBot="1">
+      <c r="A6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O6" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="150" customHeight="1" thickTop="1">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="C5:I5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.19685039370078741" bottom="0" header="0.19685039370078741" footer="0"/>
+  <pageSetup paperSize="9" scale="22" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" customWidth="1"/>
+    <col min="3" max="3" width="38.5703125" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" customWidth="1"/>
+    <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5703125" customWidth="1"/>
+    <col min="11" max="13" width="25.7109375" customWidth="1"/>
+    <col min="14" max="15" width="26.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A1" s="24"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+    </row>
+    <row r="2" spans="1:15" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="B2" s="4"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+    </row>
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="B3" s="4"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+    </row>
+    <row r="4" spans="1:15" s="1" customFormat="1" ht="77.25" customHeight="1">
+      <c r="A4" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+    </row>
+    <row r="5" spans="1:15" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+    </row>
+    <row r="6" spans="1:15" ht="105.75" customHeight="1" thickBot="1">
+      <c r="A6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O6" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="150" customHeight="1" thickTop="1">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="C5:I5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.19685039370078741" bottom="0" header="0.19685039370078741" footer="0"/>
+  <pageSetup paperSize="9" scale="22" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N7"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
@@ -2240,57 +3304,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="23"/>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="A1" s="24"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="B2" s="4"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="B3" s="4"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="77.25" customHeight="1">
-      <c r="A4" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
+      <c r="A4" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
     </row>
     <row r="6" spans="1:14" ht="105.75" customHeight="1" thickBot="1">
       <c r="A6" s="5" t="s">
@@ -2367,297 +3431,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" customWidth="1"/>
-    <col min="3" max="3" width="38.5703125" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
-    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" customWidth="1"/>
-    <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.5703125" customWidth="1"/>
-    <col min="11" max="13" width="25.7109375" customWidth="1"/>
-    <col min="14" max="14" width="26.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="23"/>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="4"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="B3" s="4"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="77.25" customHeight="1">
-      <c r="A4" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-    </row>
-    <row r="6" spans="1:14" ht="105.75" customHeight="1" thickBot="1">
-      <c r="A6" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="L6" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="M6" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="N6" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="150" customHeight="1" thickTop="1">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="C5:I5"/>
-  </mergeCells>
-  <phoneticPr fontId="19" type="noConversion"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.19685039370078741" bottom="0" header="0.19685039370078741" footer="0"/>
-  <pageSetup paperSize="9" scale="22" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" customWidth="1"/>
-    <col min="3" max="3" width="38.5703125" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
-    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" customWidth="1"/>
-    <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.5703125" customWidth="1"/>
-    <col min="11" max="13" width="25.7109375" customWidth="1"/>
-    <col min="14" max="14" width="26.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="23"/>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="4"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="B3" s="4"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="77.25" customHeight="1">
-      <c r="A4" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-    </row>
-    <row r="6" spans="1:14" ht="105.75" customHeight="1" thickBot="1">
-      <c r="A6" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="L6" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="M6" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="N6" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="150" customHeight="1" thickTop="1">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="C5:I5"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.19685039370078741" bottom="0" header="0.19685039370078741" footer="0"/>
-  <pageSetup paperSize="9" scale="22" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>